--- a/utils/insumos/regra_classificacao.xlsx
+++ b/utils/insumos/regra_classificacao.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hapvida-my.sharepoint.com/personal/anderson_dossantos_hapvida_com_br/Documents/5 Estrelas/INSUMOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anderson.dossantos\Desktop\dev\5 Estrelas\utils\insumos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_A169DBD5806D34EE6FD37FCEB9F353F2B20D6C26" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47B7D13A-2708-4B52-8F3D-F52D97B62D14}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34740E36-024F-47FC-AE2B-FCC099C45A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,28 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">regras_classificacao!$A$1:$Q$39</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="185">
   <si>
     <t>CHAVE_GRUPO</t>
   </si>
@@ -180,7 +164,10 @@
     <t>ESPECIALIDADE</t>
   </si>
   <si>
-    <t>TIPO diferente 6 | ESPECIALIDADE contem_regex sinta-se|sintase|sinta se|viver bem | CLASSIFICACAO vazia</t>
+    <t>sinta-se|sintase|sinta se|viver bem|qualivida|qualivita</t>
+  </si>
+  <si>
+    <t>TIPO diferente 6 | ESPECIALIDADE contem_regex sinta-se|sintase|sinta se|viver bem|qualivida|qualivita | CLASSIFICACAO vazia. Observacao: regra ampliada porque especialidades do programa Qualivida com TIPO 4 estavam ficando sem classificacao e depois caindo em MED PREV.</t>
   </si>
   <si>
     <t>NASCER_BEM</t>
@@ -1197,7 +1184,7 @@
         <v>36</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O7">
         <v>6</v>
@@ -1206,21 +1193,21 @@
         <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>20</v>
@@ -1241,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O8">
         <v>7</v>
@@ -1250,21 +1237,21 @@
         <v>25</v>
       </c>
       <c r="Q8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>20</v>
@@ -1285,7 +1272,7 @@
         <v>36</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1294,21 +1281,21 @@
         <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>20</v>
@@ -1329,7 +1316,7 @@
         <v>36</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O10">
         <v>9</v>
@@ -1338,21 +1325,21 @@
         <v>25</v>
       </c>
       <c r="Q10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
         <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -1373,7 +1360,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1382,21 +1369,21 @@
         <v>25</v>
       </c>
       <c r="Q11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
         <v>65</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
@@ -1417,7 +1404,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O12">
         <v>11</v>
@@ -1426,21 +1413,21 @@
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
@@ -1461,7 +1448,7 @@
         <v>36</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O13">
         <v>12</v>
@@ -1470,21 +1457,21 @@
         <v>25</v>
       </c>
       <c r="Q13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
         <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
@@ -1505,7 +1492,7 @@
         <v>36</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O14">
         <v>13</v>
@@ -1514,21 +1501,21 @@
         <v>25</v>
       </c>
       <c r="Q14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
@@ -1549,7 +1536,7 @@
         <v>36</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O15">
         <v>14</v>
@@ -1558,21 +1545,21 @@
         <v>25</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
@@ -1593,7 +1580,7 @@
         <v>36</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O16">
         <v>15</v>
@@ -1602,21 +1589,21 @@
         <v>25</v>
       </c>
       <c r="Q16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
@@ -1637,7 +1624,7 @@
         <v>36</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O17">
         <v>16</v>
@@ -1646,21 +1633,21 @@
         <v>25</v>
       </c>
       <c r="Q17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
@@ -1681,7 +1668,7 @@
         <v>36</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O18">
         <v>17</v>
@@ -1690,18 +1677,18 @@
         <v>25</v>
       </c>
       <c r="Q18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
         <v>25</v>
@@ -1722,18 +1709,18 @@
         <v>25</v>
       </c>
       <c r="Q19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
         <v>25</v>
@@ -1754,18 +1741,18 @@
         <v>25</v>
       </c>
       <c r="Q20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>25</v>
@@ -1795,18 +1782,18 @@
         <v>25</v>
       </c>
       <c r="Q21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
@@ -1836,21 +1823,21 @@
         <v>25</v>
       </c>
       <c r="Q22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
@@ -1880,30 +1867,30 @@
         <v>36</v>
       </c>
       <c r="N23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O23">
         <v>22</v>
       </c>
       <c r="P23" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E24" t="s">
         <v>25</v>
@@ -1924,7 +1911,7 @@
         <v>36</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O24">
         <v>23</v>
@@ -1933,18 +1920,18 @@
         <v>25</v>
       </c>
       <c r="Q24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>25</v>
@@ -1974,18 +1961,18 @@
         <v>25</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
@@ -2006,21 +1993,21 @@
         <v>25</v>
       </c>
       <c r="Q26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
         <v>20</v>
@@ -2032,7 +2019,7 @@
         <v>36</v>
       </c>
       <c r="H27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I27" t="s">
         <v>21</v>
@@ -2050,21 +2037,21 @@
         <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -2094,18 +2081,18 @@
         <v>25</v>
       </c>
       <c r="Q28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
         <v>25</v>
@@ -2135,21 +2122,21 @@
         <v>25</v>
       </c>
       <c r="Q29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
@@ -2179,18 +2166,18 @@
         <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
@@ -2220,18 +2207,18 @@
         <v>25</v>
       </c>
       <c r="Q31" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
@@ -2261,18 +2248,18 @@
         <v>25</v>
       </c>
       <c r="Q32" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
@@ -2302,18 +2289,18 @@
         <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
@@ -2343,18 +2330,18 @@
         <v>25</v>
       </c>
       <c r="Q34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
@@ -2363,10 +2350,10 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s">
         <v>23</v>
@@ -2384,18 +2371,18 @@
         <v>25</v>
       </c>
       <c r="Q35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
@@ -2404,10 +2391,10 @@
         <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I36" t="s">
         <v>23</v>
@@ -2425,18 +2412,18 @@
         <v>25</v>
       </c>
       <c r="Q36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
@@ -2457,21 +2444,21 @@
         <v>25</v>
       </c>
       <c r="Q37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
         <v>21</v>
@@ -2489,21 +2476,21 @@
         <v>25</v>
       </c>
       <c r="Q38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39" t="s">
         <v>25</v>
@@ -2518,13 +2505,13 @@
         <v>5</v>
       </c>
       <c r="I39" t="s">
+        <v>166</v>
+      </c>
+      <c r="J39" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="J39" t="s">
-        <v>22</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="O39">
         <v>38</v>
@@ -2533,7 +2520,7 @@
         <v>25</v>
       </c>
       <c r="Q39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2544,8 +2531,8 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;KFF0000 INTERNO&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;KFF0000 INTERNO</oddFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;1 &amp;KFF0000 INTERNO#_x000D_</oddHeader>
+    <oddFooter>&amp;C&amp;"Aptos"&amp;10 &amp;KFF0000_x000D_# INTERNO</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2561,7 +2548,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>16</v>
@@ -2572,7 +2559,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2580,39 +2567,39 @@
         <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2620,39 +2607,39 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;KFF0000 INTERNO&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;KFF0000 INTERNO</oddFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;1 &amp;KFF0000 INTERNO#_x000D_</oddHeader>
+    <oddFooter>&amp;C&amp;"Aptos"&amp;10 &amp;KFF0000_x000D_# INTERNO</oddFooter>
   </headerFooter>
 </worksheet>
 </file>